--- a/Chenda.xlsx
+++ b/Chenda.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahul\Desktop\CODING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EBCF11-1540-4E26-8B65-0BD4E938435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87910889-5F2D-4A1F-A997-58DA04C8946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99AB6E6A-85BA-4F0A-A1B5-9EF41BDE36B0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -316,54 +316,6 @@
   </si>
   <si>
     <t>14 Months</t>
-  </si>
-  <si>
-    <t>05.04.2024</t>
-  </si>
-  <si>
-    <t>04.15.2023</t>
-  </si>
-  <si>
-    <t>04.22.2023</t>
-  </si>
-  <si>
-    <t>04.30.2023</t>
-  </si>
-  <si>
-    <t>01.06.2023</t>
-  </si>
-  <si>
-    <t>01.06.2024</t>
-  </si>
-  <si>
-    <t>05.11.2024</t>
-  </si>
-  <si>
-    <t>06.18.2023</t>
-  </si>
-  <si>
-    <t>05.05.2023</t>
-  </si>
-  <si>
-    <t>05.06.2023</t>
-  </si>
-  <si>
-    <t>07.07.2024</t>
-  </si>
-  <si>
-    <t>06.04.2023</t>
-  </si>
-  <si>
-    <t>05.08.2024</t>
-  </si>
-  <si>
-    <t>04.06.2023</t>
-  </si>
-  <si>
-    <t>06.01.2023</t>
-  </si>
-  <si>
-    <t>08.27.2023</t>
   </si>
 </sst>
 </file>
@@ -371,7 +323,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm\.dd\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -431,7 +383,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +452,7 @@
         </row>
         <row r="6">
           <cell r="AL6">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="AM6">
             <v>8</v>
@@ -732,7 +684,7 @@
         </row>
         <row r="35">
           <cell r="AL35">
-            <v>7</v>
+            <v>10</v>
           </cell>
           <cell r="AM35">
             <v>3</v>
@@ -740,7 +692,7 @@
         </row>
         <row r="36">
           <cell r="AL36">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="AM36">
             <v>6</v>
@@ -748,7 +700,7 @@
         </row>
         <row r="37">
           <cell r="AL37">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="AM37">
             <v>6</v>
@@ -1361,8 +1313,8 @@
       <c r="B2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>93</v>
+      <c r="C2" s="6">
+        <v>45416</v>
       </c>
       <c r="D2" s="4">
         <v>1001</v>
@@ -1392,8 +1344,8 @@
       <c r="B3" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>94</v>
+      <c r="C3" s="6">
+        <v>45031</v>
       </c>
       <c r="D3" s="4">
         <v>1002</v>
@@ -1423,8 +1375,8 @@
       <c r="B4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>95</v>
+      <c r="C4" s="6">
+        <v>45038</v>
       </c>
       <c r="D4" s="4">
         <v>1003</v>
@@ -1448,8 +1400,8 @@
       <c r="B5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>94</v>
+      <c r="C5" s="6">
+        <v>45031</v>
       </c>
       <c r="D5" s="4">
         <v>1004</v>
@@ -1459,7 +1411,7 @@
       </c>
       <c r="F5" s="4">
         <f>[1]STUDENTS!AL6</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4">
         <f>[1]STUDENTS!AM6</f>
@@ -1479,8 +1431,8 @@
       <c r="B6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>95</v>
+      <c r="C6" s="6">
+        <v>45038</v>
       </c>
       <c r="D6" s="4">
         <v>1005</v>
@@ -1510,8 +1462,8 @@
       <c r="B7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>94</v>
+      <c r="C7" s="6">
+        <v>45031</v>
       </c>
       <c r="D7" s="4">
         <v>1006</v>
@@ -1535,8 +1487,8 @@
       <c r="B8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>94</v>
+      <c r="C8" s="6">
+        <v>45031</v>
       </c>
       <c r="D8" s="4">
         <v>1007</v>
@@ -1560,8 +1512,8 @@
       <c r="B9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>96</v>
+      <c r="C9" s="6">
+        <v>45046</v>
       </c>
       <c r="D9" s="4">
         <v>1008</v>
@@ -1585,8 +1537,8 @@
       <c r="B10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>96</v>
+      <c r="C10" s="6">
+        <v>45046</v>
       </c>
       <c r="D10" s="4">
         <v>1009</v>
@@ -1610,8 +1562,8 @@
       <c r="B11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>96</v>
+      <c r="C11" s="6">
+        <v>45046</v>
       </c>
       <c r="D11" s="4">
         <v>1010</v>
@@ -1635,8 +1587,8 @@
       <c r="B12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>94</v>
+      <c r="C12" s="6">
+        <v>45031</v>
       </c>
       <c r="D12" s="4">
         <v>1011</v>
@@ -1666,8 +1618,8 @@
       <c r="B13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>94</v>
+      <c r="C13" s="6">
+        <v>45031</v>
       </c>
       <c r="D13" s="4">
         <v>1012</v>
@@ -1691,8 +1643,8 @@
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>95</v>
+      <c r="C14" s="6">
+        <v>45038</v>
       </c>
       <c r="D14" s="4">
         <v>1013</v>
@@ -1716,8 +1668,8 @@
       <c r="B15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>98</v>
+      <c r="C15" s="6">
+        <v>45297</v>
       </c>
       <c r="D15" s="4">
         <v>1014</v>
@@ -1741,8 +1693,8 @@
       <c r="B16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>99</v>
+      <c r="C16" s="6">
+        <v>45423</v>
       </c>
       <c r="D16" s="4">
         <v>1015</v>
@@ -1766,8 +1718,8 @@
       <c r="B17" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>96</v>
+      <c r="C17" s="6">
+        <v>45046</v>
       </c>
       <c r="D17" s="4">
         <v>1016</v>
@@ -1791,8 +1743,8 @@
       <c r="B18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>94</v>
+      <c r="C18" s="6">
+        <v>45031</v>
       </c>
       <c r="D18" s="4">
         <v>1017</v>
@@ -1816,8 +1768,8 @@
       <c r="B19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>95</v>
+      <c r="C19" s="6">
+        <v>45038</v>
       </c>
       <c r="D19" s="4">
         <v>1018</v>
@@ -1841,8 +1793,8 @@
       <c r="B20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>94</v>
+      <c r="C20" s="6">
+        <v>45031</v>
       </c>
       <c r="D20" s="4">
         <v>1019</v>
@@ -1866,8 +1818,8 @@
       <c r="B21" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>94</v>
+      <c r="C21" s="6">
+        <v>45031</v>
       </c>
       <c r="D21" s="4">
         <v>1020</v>
@@ -1891,8 +1843,8 @@
       <c r="B22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>96</v>
+      <c r="C22" s="6">
+        <v>45046</v>
       </c>
       <c r="D22" s="4">
         <v>1021</v>
@@ -1922,8 +1874,8 @@
       <c r="B23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>94</v>
+      <c r="C23" s="6">
+        <v>45031</v>
       </c>
       <c r="D23" s="4">
         <v>1022</v>
@@ -1953,8 +1905,8 @@
       <c r="B24" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>100</v>
+      <c r="C24" s="6">
+        <v>45095</v>
       </c>
       <c r="D24" s="4">
         <v>1023</v>
@@ -1978,8 +1930,8 @@
       <c r="B25" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>95</v>
+      <c r="C25" s="6">
+        <v>45038</v>
       </c>
       <c r="D25" s="4">
         <v>1024</v>
@@ -2003,8 +1955,8 @@
       <c r="B26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>96</v>
+      <c r="C26" s="6">
+        <v>45046</v>
       </c>
       <c r="D26" s="4">
         <v>1025</v>
@@ -2028,8 +1980,8 @@
       <c r="B27" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>94</v>
+      <c r="C27" s="6">
+        <v>45031</v>
       </c>
       <c r="D27" s="4">
         <v>1026</v>
@@ -2053,8 +2005,8 @@
       <c r="B28" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>105</v>
+      <c r="C28" s="6">
+        <v>45420</v>
       </c>
       <c r="D28" s="4">
         <v>1027</v>
@@ -2084,8 +2036,8 @@
       <c r="B29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>95</v>
+      <c r="C29" s="6">
+        <v>45038</v>
       </c>
       <c r="D29" s="4">
         <v>1028</v>
@@ -2115,8 +2067,8 @@
       <c r="B30" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>97</v>
+      <c r="C30" s="6">
+        <v>45297</v>
       </c>
       <c r="D30" s="4">
         <v>1029</v>
@@ -2146,8 +2098,8 @@
       <c r="B31" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>94</v>
+      <c r="C31" s="6">
+        <v>45031</v>
       </c>
       <c r="D31" s="4">
         <v>1030</v>
@@ -2171,8 +2123,8 @@
       <c r="B32" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>94</v>
+      <c r="C32" s="6">
+        <v>45031</v>
       </c>
       <c r="D32" s="4">
         <v>1031</v>
@@ -2196,8 +2148,8 @@
       <c r="B33" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>94</v>
+      <c r="C33" s="6">
+        <v>45031</v>
       </c>
       <c r="D33" s="4">
         <v>1032</v>
@@ -2227,8 +2179,8 @@
       <c r="B34" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>94</v>
+      <c r="C34" s="6">
+        <v>45031</v>
       </c>
       <c r="D34" s="4">
         <v>1033</v>
@@ -2238,17 +2190,17 @@
       </c>
       <c r="F34" s="4">
         <f>[1]STUDENTS!AL35</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4">
         <f>[1]STUDENTS!AM35</f>
         <v>3</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I34" s="5">
-        <v>3600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2258,8 +2210,8 @@
       <c r="B35" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>94</v>
+      <c r="C35" s="6">
+        <v>45031</v>
       </c>
       <c r="D35" s="4">
         <v>1034</v>
@@ -2269,7 +2221,7 @@
       </c>
       <c r="F35" s="4">
         <f>[1]STUDENTS!AL36</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" s="4">
         <f>[1]STUDENTS!AM36</f>
@@ -2289,8 +2241,8 @@
       <c r="B36" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>94</v>
+      <c r="C36" s="6">
+        <v>45031</v>
       </c>
       <c r="D36" s="4">
         <v>1035</v>
@@ -2300,7 +2252,7 @@
       </c>
       <c r="F36" s="4">
         <f>[1]STUDENTS!AL37</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4">
         <f>[1]STUDENTS!AM37</f>
@@ -2320,8 +2272,8 @@
       <c r="B37" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>94</v>
+      <c r="C37" s="6">
+        <v>45031</v>
       </c>
       <c r="D37" s="4">
         <v>1036</v>
@@ -2345,8 +2297,8 @@
       <c r="B38" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>94</v>
+      <c r="C38" s="6">
+        <v>45031</v>
       </c>
       <c r="D38" s="4">
         <v>1037</v>
@@ -2370,8 +2322,8 @@
       <c r="B39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>108</v>
+      <c r="C39" s="6">
+        <v>45165</v>
       </c>
       <c r="D39" s="4">
         <v>1038</v>
@@ -2395,8 +2347,8 @@
       <c r="B40" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>100</v>
+      <c r="C40" s="6">
+        <v>45095</v>
       </c>
       <c r="D40" s="4">
         <v>1039</v>
@@ -2426,8 +2378,8 @@
       <c r="B41" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>94</v>
+      <c r="C41" s="6">
+        <v>45031</v>
       </c>
       <c r="D41" s="4">
         <v>1040</v>
@@ -2457,8 +2409,8 @@
       <c r="B42" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>96</v>
+      <c r="C42" s="6">
+        <v>45046</v>
       </c>
       <c r="D42" s="4">
         <v>1041</v>
@@ -2482,8 +2434,8 @@
       <c r="B43" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>107</v>
+      <c r="C43" s="6">
+        <v>45078</v>
       </c>
       <c r="D43" s="4">
         <v>1042</v>
@@ -2507,8 +2459,8 @@
       <c r="B44" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>94</v>
+      <c r="C44" s="6">
+        <v>45031</v>
       </c>
       <c r="D44" s="4">
         <v>1043</v>
@@ -2532,8 +2484,8 @@
       <c r="B45" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>96</v>
+      <c r="C45" s="6">
+        <v>45046</v>
       </c>
       <c r="D45" s="4">
         <v>1044</v>
@@ -2557,8 +2509,8 @@
       <c r="B46" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>106</v>
+      <c r="C46" s="6">
+        <v>45022</v>
       </c>
       <c r="D46" s="4">
         <v>1045</v>
@@ -2582,8 +2534,8 @@
       <c r="B47" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>94</v>
+      <c r="C47" s="6">
+        <v>45031</v>
       </c>
       <c r="D47" s="4">
         <v>1046</v>
@@ -2613,8 +2565,8 @@
       <c r="B48" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>96</v>
+      <c r="C48" s="6">
+        <v>45046</v>
       </c>
       <c r="D48" s="4">
         <v>1047</v>
@@ -2644,8 +2596,8 @@
       <c r="B49" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>103</v>
+      <c r="C49" s="6">
+        <v>45480</v>
       </c>
       <c r="D49" s="4">
         <v>1048</v>
@@ -2675,8 +2627,8 @@
       <c r="B50" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>94</v>
+      <c r="C50" s="6">
+        <v>45031</v>
       </c>
       <c r="D50" s="4">
         <v>1049</v>
@@ -2706,8 +2658,8 @@
       <c r="B51" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>95</v>
+      <c r="C51" s="6">
+        <v>45038</v>
       </c>
       <c r="D51" s="4">
         <v>1050</v>
@@ -2731,8 +2683,8 @@
       <c r="B52" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>96</v>
+      <c r="C52" s="6">
+        <v>45046</v>
       </c>
       <c r="D52" s="4">
         <v>1051</v>
@@ -2762,8 +2714,8 @@
       <c r="B53" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>105</v>
+      <c r="C53" s="6">
+        <v>45420</v>
       </c>
       <c r="D53" s="4">
         <v>1052</v>
@@ -2793,8 +2745,8 @@
       <c r="B54" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>103</v>
+      <c r="C54" s="6">
+        <v>45480</v>
       </c>
       <c r="D54" s="4">
         <v>1053</v>
@@ -2818,8 +2770,8 @@
       <c r="B55" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>96</v>
+      <c r="C55" s="6">
+        <v>45046</v>
       </c>
       <c r="D55" s="4">
         <v>1054</v>
@@ -2849,8 +2801,8 @@
       <c r="B56" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>95</v>
+      <c r="C56" s="6">
+        <v>45038</v>
       </c>
       <c r="D56" s="4">
         <v>1055</v>
@@ -2874,8 +2826,8 @@
       <c r="B57" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>94</v>
+      <c r="C57" s="6">
+        <v>45031</v>
       </c>
       <c r="D57" s="4">
         <v>1056</v>
@@ -2899,8 +2851,8 @@
       <c r="B58" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>94</v>
+      <c r="C58" s="6">
+        <v>45031</v>
       </c>
       <c r="D58" s="4">
         <v>1057</v>
@@ -2924,8 +2876,8 @@
       <c r="B59" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>102</v>
+      <c r="C59" s="6">
+        <v>45052</v>
       </c>
       <c r="D59" s="4">
         <v>1058</v>
@@ -2949,8 +2901,8 @@
       <c r="B60" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>94</v>
+      <c r="C60" s="6">
+        <v>45031</v>
       </c>
       <c r="D60" s="4">
         <v>1059</v>
@@ -2974,8 +2926,8 @@
       <c r="B61" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>94</v>
+      <c r="C61" s="6">
+        <v>45031</v>
       </c>
       <c r="D61" s="4">
         <v>1060</v>
@@ -3005,8 +2957,8 @@
       <c r="B62" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>101</v>
+      <c r="C62" s="6">
+        <v>45417</v>
       </c>
       <c r="D62" s="4">
         <v>1061</v>
@@ -3036,8 +2988,8 @@
       <c r="B63" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>96</v>
+      <c r="C63" s="6">
+        <v>45046</v>
       </c>
       <c r="D63" s="4">
         <v>1062</v>
@@ -3067,8 +3019,8 @@
       <c r="B64" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>94</v>
+      <c r="C64" s="6">
+        <v>45031</v>
       </c>
       <c r="D64" s="4">
         <v>1063</v>
@@ -3092,8 +3044,8 @@
       <c r="B65" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>104</v>
+      <c r="C65" s="6">
+        <v>45081</v>
       </c>
       <c r="D65" s="4">
         <v>1064</v>
@@ -3123,8 +3075,8 @@
       <c r="B66" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>101</v>
+      <c r="C66" s="6">
+        <v>45417</v>
       </c>
       <c r="D66" s="4">
         <v>1065</v>
@@ -3154,8 +3106,8 @@
       <c r="B67" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>103</v>
+      <c r="C67" s="6">
+        <v>45480</v>
       </c>
       <c r="D67" s="4">
         <v>1066</v>

--- a/Chenda.xlsx
+++ b/Chenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahul\Desktop\CODING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87910889-5F2D-4A1F-A997-58DA04C8946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB36440A-9E86-4E2F-825D-63A96BEEE9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99AB6E6A-85BA-4F0A-A1B5-9EF41BDE36B0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -323,7 +323,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -383,7 +383,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,7 +748,7 @@
         </row>
         <row r="43">
           <cell r="AL43">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="AM43">
             <v>10</v>
@@ -2420,11 +2420,17 @@
       </c>
       <c r="F42" s="4">
         <f>[1]STUDENTS!AL43</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G42" s="4">
         <f>[1]STUDENTS!AM43</f>
         <v>10</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I42" s="5">
+        <v>1500</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
